--- a/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
+++ b/InputData/elec/GBSC/Grid Battery Storage Capacities.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/KY/elec/GBSC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\KY\elec\GBSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6867A922-1BC8-6345-9472-A2CF1BB44576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{877870FE-44B1-48D5-AE0B-D3C5216C1619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32740" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="975" windowWidth="16290" windowHeight="17025" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,13 @@
     <sheet name="BGBSC" sheetId="5" r:id="rId6"/>
     <sheet name="PAGBSC" sheetId="6" r:id="rId7"/>
     <sheet name="SYGBSC" sheetId="7" r:id="rId8"/>
+    <sheet name="GBDSD" sheetId="12" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
+    <definedName name="gigwatts_to_megawatts" localSheetId="8">About!$A$42</definedName>
     <definedName name="gigwatts_to_megawatts" localSheetId="4">[1]About!$A$35</definedName>
     <definedName name="gigwatts_to_megawatts">About!#REF!</definedName>
   </definedNames>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="159">
   <si>
     <t>GBSC BAU Grid Battery Storage Capacity</t>
   </si>
@@ -513,6 +515,15 @@
   </si>
   <si>
     <t>Fraction</t>
+  </si>
+  <si>
+    <t>Unit: hours</t>
+  </si>
+  <si>
+    <t>hours</t>
+  </si>
+  <si>
+    <t>hours per day battery may charge and discharge</t>
   </si>
 </sst>
 </file>
@@ -1033,27 +1044,19 @@
       <alignment wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1062,6 +1065,12 @@
     <xf numFmtId="0" fontId="26" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="58">
     <cellStyle name="20% - Accent1 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1186,7 +1195,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="About"/>
@@ -1215,9 +1224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1255,9 +1264,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1290,26 +1299,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1342,26 +1334,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1536,506 +1511,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="54" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="23">
-        <v>44874</v>
-      </c>
-      <c r="F1" s="22" t="s">
+      <c r="C1" s="17">
+        <v>45187</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" t="str">
         <f>LOOKUP(B1,F1:G50,G1:G50)</f>
         <v>KY</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F4" s="22" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="16" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
         <v>2020</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="16" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F11" s="22" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="16" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="7"/>
-      <c r="F18" s="22" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="6"/>
+      <c r="F18" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="6">
         <v>2018</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="7"/>
-      <c r="F25" s="22" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+      <c r="F25" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="F26" s="22" t="s">
+      <c r="B26" s="6"/>
+      <c r="F26" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>145</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="G27" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>146</v>
       </c>
-      <c r="F28" s="22" t="s">
+      <c r="F28" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F29" s="22" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F29" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="G29" s="22" t="s">
+      <c r="G29" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>147</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="16" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="16" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F32" s="22" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F32" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="22" t="s">
+      <c r="G32" s="16" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F33" s="22" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F33" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="F34" s="22" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="F34" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="7"/>
-      <c r="F35" s="22" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="F35" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F36" s="22" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F36" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F37" s="22" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F37" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G37" s="22" t="s">
+      <c r="G37" s="16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F38" s="22" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F38" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="G38" s="22" t="s">
+      <c r="G38" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F39" s="22" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F39" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F40" s="22" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F40" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="G40" s="22" t="s">
+      <c r="G40" s="16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F41" s="22" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F41" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="G41" s="22" t="s">
+      <c r="G41" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F42" s="22" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F42" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="G42" s="22" t="s">
+      <c r="G42" s="16" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F43" s="22" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F43" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="G43" s="22" t="s">
+      <c r="G43" s="16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F44" s="22" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F44" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F45" s="22" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F45" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F46" s="22" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F46" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F47" s="22" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F47" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="G47" s="22" t="s">
+      <c r="G47" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F48" s="22" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F48" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="49" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F49" s="22" t="s">
+    <row r="49" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F49" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G49" s="22" t="s">
+      <c r="G49" s="16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="6:7" x14ac:dyDescent="0.2">
-      <c r="F50" s="22" t="s">
+    <row r="50" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F50" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="G50" s="22" t="s">
+      <c r="G50" s="16" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2053,1116 +2027,1111 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D552774A-08E8-3A40-B065-9B2521BECE85}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="3"/>
-      <c r="B1" s="13">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="8">
         <v>2019</v>
       </c>
-      <c r="C1" s="14">
+      <c r="C1" s="9">
         <v>2035</v>
       </c>
-      <c r="D1" s="14">
+      <c r="D1" s="9">
         <v>2050</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="7">
         <v>1</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="7">
         <v>4191.3008906650002</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="7">
         <v>9203.6684837369994</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="10">
         <f>C3/C$51</f>
         <v>2.8397041537024457E-2</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="10">
         <f>D3/D$51</f>
         <v>2.6756725886505798E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="7">
         <v>0</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="7">
         <v>1379.102465835</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="7">
         <v>3764.7381143699999</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="10">
         <f t="shared" ref="E4:E50" si="0">C4/$C$51</f>
         <v>9.3437410073214187E-3</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="10">
         <f t="shared" ref="F4:F50" si="1">D4/D$51</f>
         <v>1.0944773373647004E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="7">
         <v>78.301225951000006</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="7">
         <v>4292.7729009180002</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="7">
         <v>7708.9502813700001</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="10">
         <f t="shared" si="0"/>
         <v>2.9084538084079237E-2</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="10">
         <f t="shared" si="1"/>
         <v>2.2411310220027372E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="7">
         <v>444.98</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="7">
         <v>13496.128078713</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="7">
         <v>21861.061091347001</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="10">
         <f t="shared" si="0"/>
         <v>9.1439416934680606E-2</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="10">
         <f t="shared" si="1"/>
         <v>6.3554051326697447E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="7">
         <v>2907.4880079579998</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="7">
         <v>5465.1997496209997</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="10">
         <f t="shared" si="0"/>
         <v>1.9698909690371583E-2</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="10">
         <f t="shared" si="1"/>
         <v>1.5888322343856801E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="7">
         <v>1.6</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="7">
         <v>18.641403977</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="7">
         <v>701.90923692299998</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="10">
         <f t="shared" si="0"/>
         <v>1.2629986174992377E-4</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="10">
         <f t="shared" si="1"/>
         <v>2.0405768724439683E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="7">
         <v>0</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="7">
         <v>307.79480332999998</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="7">
         <v>1318.2366882209999</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="10">
         <f t="shared" si="0"/>
         <v>2.0853816137393808E-3</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="10">
         <f t="shared" si="1"/>
         <v>3.8323520433824884E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="7">
         <v>14</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="7">
         <v>6634.4589765290002</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="7">
         <v>16108.682616767001</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="10">
         <f t="shared" si="0"/>
         <v>4.4950007657953428E-2</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="10">
         <f t="shared" si="1"/>
         <v>4.6830848582949905E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="7">
         <v>1</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="7">
         <v>1840.525499907</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="7">
         <v>13217.018615075</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="10">
         <f t="shared" si="0"/>
         <v>1.2469989732118525E-2</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="10">
         <f t="shared" si="1"/>
         <v>3.8424259277189309E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="7">
         <v>0</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="7">
         <v>4043.3463704350002</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="7">
         <v>10452.413944238</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="10">
         <f t="shared" si="0"/>
         <v>2.7394615138595393E-2</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="10">
         <f t="shared" si="1"/>
         <v>3.0387054385156501E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="7">
         <v>3.090607484</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="7">
         <v>3292.5474433149998</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="7">
         <v>8588.1790860540004</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="10">
         <f t="shared" si="0"/>
         <v>2.2307777215108279E-2</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="10">
         <f t="shared" si="1"/>
         <v>2.4967387088725916E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="7">
         <v>112.4</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="7">
         <v>5782.3560435359996</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="7">
         <v>11905.713153897999</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="10">
         <f t="shared" si="0"/>
         <v>3.917681145628836E-2</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="10">
         <f t="shared" si="1"/>
         <v>3.4612057562167856E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="7">
         <v>23</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="7">
         <v>4755.249369225</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="7">
         <v>14321.589911745999</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="10">
         <f t="shared" si="0"/>
         <v>3.2217924071627969E-2</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="10">
         <f t="shared" si="1"/>
         <v>4.1635447452790346E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="7">
         <v>0</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="7">
         <v>3439.6907645870001</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="7">
         <v>1648.040011523</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="10">
         <f t="shared" si="0"/>
         <v>2.3304707551310835E-2</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="10">
         <f t="shared" si="1"/>
         <v>4.7911498459807886E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="7">
         <v>0</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="7">
         <v>4108.4553061839997</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="7">
         <v>11301.080228199</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="10">
         <f t="shared" si="0"/>
         <v>2.783574337088569E-2</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="10">
         <f t="shared" si="1"/>
         <v>3.285428048844221E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="7">
         <v>0.5</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="7">
         <v>2830.9170737869999</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="7">
         <v>8099.078065011</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="10">
         <f t="shared" si="0"/>
         <v>1.918012374421689E-2</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="10">
         <f t="shared" si="1"/>
         <v>2.3545482119638632E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="7">
         <v>29.5</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="7">
         <v>50</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="7">
         <v>3361.3766189789999</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="10">
         <f t="shared" si="0"/>
         <v>3.3876166705510525E-4</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="10">
         <f t="shared" si="1"/>
         <v>9.7721286848015954E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="7">
         <v>13</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="7">
         <v>1387.2392184830001</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="7">
         <v>8943.7276795229991</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="10">
         <f t="shared" si="0"/>
         <v>9.3988694051504486E-3</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="10">
         <f t="shared" si="1"/>
         <v>2.6001031039677953E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="7">
         <v>16.2</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="7">
         <v>51.830478356</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="7">
         <v>164.90325891099999</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="10">
         <f t="shared" si="0"/>
         <v>3.5116358504284223E-4</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="10">
         <f t="shared" si="1"/>
         <v>4.7940354482233486E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="7">
         <v>1</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="7">
         <v>4630.261240754</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="7">
         <v>11031.483067769999</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="10">
         <f t="shared" si="0"/>
         <v>3.1371100336369299E-2</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="10">
         <f t="shared" si="1"/>
         <v>3.2070512870766121E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="7">
         <v>1</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="7">
         <v>1044.3894318099999</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="7">
         <v>3874.3181162430001</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="10">
         <f t="shared" si="0"/>
         <v>7.075982099493794E-3</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="10">
         <f t="shared" si="1"/>
         <v>1.1263342222355487E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="7">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="7">
         <v>2109.9074876519999</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="7">
         <v>8556.8961626460004</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="10">
         <f t="shared" si="0"/>
         <v>1.4295115556980808E-2</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="10">
         <f t="shared" si="1"/>
         <v>2.4876441982648326E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="7">
         <v>0</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="7">
         <v>1321.125902582</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="7">
         <v>4790.0051287730003</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="10">
         <f t="shared" si="0"/>
         <v>8.9509362629671772E-3</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="10">
         <f t="shared" si="1"/>
         <v>1.3925409683324102E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="7">
         <v>0</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="7">
         <v>1029.8705014919999</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="7">
         <v>2836.690723278</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="10">
         <f t="shared" si="0"/>
         <v>6.977612958726143E-3</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="10">
         <f t="shared" si="1"/>
         <v>8.2467720606908615E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="7">
         <v>1</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="7">
         <v>5956.9820277979998</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="7">
         <v>17741.490234403998</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="10">
         <f t="shared" si="0"/>
         <v>4.035994324708303E-2</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="10">
         <f t="shared" si="1"/>
         <v>5.1577715109890766E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="7">
         <v>0</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="7">
         <v>956.60528948000001</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="7">
         <v>670.84350910700005</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="10">
         <f t="shared" si="0"/>
         <v>6.4812240515595265E-3</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="10">
         <f t="shared" si="1"/>
         <v>1.9502631931642026E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="7">
         <v>0</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="7">
         <v>1334.833530953</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="7">
         <v>1205.537881186</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="10">
         <f t="shared" si="0"/>
         <v>9.0438086437338149E-3</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="10">
         <f t="shared" si="1"/>
         <v>3.5047162650078062E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="7">
         <v>0</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="7">
         <v>77.076554481000002</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="7">
         <v>652.162611481</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="10">
         <f t="shared" si="0"/>
         <v>5.2221164173694404E-4</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="10">
         <f t="shared" si="1"/>
         <v>1.8959544511689881E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="7">
         <v>320.8</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="7">
         <v>2000</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="7">
         <v>2000</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="10">
         <f t="shared" si="0"/>
         <v>1.3550466682204209E-2</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="10">
         <f t="shared" si="1"/>
         <v>5.8143610743444912E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="7">
         <v>3.6</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="7">
         <v>3606.8894232070002</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="7">
         <v>3835.8916611250002</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="10">
         <f t="shared" si="0"/>
         <v>2.4437517477780606E-2</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="10">
         <f t="shared" si="1"/>
         <v>1.1151629579923916E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="7">
         <v>10</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="7">
         <v>1972.6482485649999</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="7">
         <v>3229.4136016379998</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="10">
         <f t="shared" si="0"/>
         <v>1.3365152183944259E-2</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="10">
         <f t="shared" si="1"/>
         <v>9.3884883691613165E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="7">
         <v>254</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="7">
         <v>3000</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="7">
         <v>5515.5398926870002</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="10">
         <f t="shared" si="0"/>
         <v>2.0325700023306314E-2</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="10">
         <f t="shared" si="1"/>
         <v>1.6034670228016742E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="7">
         <v>53</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="7">
         <v>12854.389578185999</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="7">
         <v>17308.154714854001</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="10">
         <f t="shared" si="0"/>
         <v>8.7091488849641199E-2</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="10">
         <f t="shared" si="1"/>
         <v>5.0317930521389588E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="7">
         <v>0</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="7">
         <v>3538.8416595570002</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="7">
         <v>5278.7681304799999</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="10">
         <f t="shared" si="0"/>
         <v>2.397647800071169E-2</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="10">
         <f t="shared" si="1"/>
         <v>1.5346331969176577E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="7">
         <v>30.135111714000001</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="7">
         <v>2195.1191461859999</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="7">
         <v>4961.7464102920003</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="10">
         <f t="shared" si="0"/>
         <v>1.4872444426930972E-2</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="10">
         <f t="shared" si="1"/>
         <v>1.4424692594385159E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="7">
         <v>30.4</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="7">
         <v>1529.7567533890001</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="7">
         <v>6240.8166906160004</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="10">
         <f t="shared" si="0"/>
         <v>1.0364458959337264E-2</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="10">
         <f t="shared" si="1"/>
         <v>1.8143180819018539E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="7">
         <v>0</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="7">
         <v>18.131715634999999</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="7">
         <v>797.33633961099997</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="10">
         <f t="shared" si="0"/>
         <v>1.2284660430163431E-4</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="10">
         <f t="shared" si="1"/>
         <v>2.318000688097259E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="7">
         <v>4</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="7">
         <v>2829.2267153779999</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="7">
         <v>11525.565173270999</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="10">
         <f t="shared" si="0"/>
         <v>1.9168671171565819E-2</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="10">
         <f t="shared" si="1"/>
         <v>3.3506898751643713E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="7">
         <v>0</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="7">
         <v>885.93782039300004</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="7">
         <v>1370.182233798</v>
       </c>
-      <c r="E41" s="16">
+      <c r="E41" s="10">
         <f t="shared" si="0"/>
         <v>6.0024354588699824E-3</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="10">
         <f t="shared" si="1"/>
         <v>3.9833671224767369E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="7">
         <v>0</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="7">
         <v>680.13968375299999</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="7">
         <v>4281.9844957329997</v>
       </c>
-      <c r="E42" s="16">
+      <c r="E42" s="10">
         <f t="shared" si="0"/>
         <v>4.6081050619699668E-3</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="10">
         <f t="shared" si="1"/>
         <v>1.244850198646829E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="7">
         <v>105.2</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="7">
         <v>20906.218037183</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="7">
         <v>37489.831749279998</v>
       </c>
-      <c r="E43" s="16">
+      <c r="E43" s="10">
         <f t="shared" si="0"/>
         <v>0.14164450548187246</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="10">
         <f t="shared" si="1"/>
         <v>0.10898970920336894</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="7">
         <v>0</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="7">
         <v>516.27327122400004</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="7">
         <v>1050.0330405249999</v>
       </c>
-      <c r="E44" s="16">
+      <c r="E44" s="10">
         <f t="shared" si="0"/>
         <v>3.497871880316695E-3</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="10">
         <f t="shared" si="1"/>
         <v>3.0526356188020757E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="7">
         <v>0</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="7">
         <v>553.27178359000004</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="7">
         <v>5983.4257381739999</v>
       </c>
-      <c r="E45" s="16">
+      <c r="E45" s="10">
         <f t="shared" si="0"/>
         <v>3.7485454348699966E-3</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="10">
         <f t="shared" si="1"/>
         <v>1.7394898851634928E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="7">
         <v>2</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="7">
         <v>0</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="7">
         <v>46.358535944000003</v>
       </c>
-      <c r="E46" s="16">
+      <c r="E46" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="10">
         <f t="shared" si="1"/>
         <v>1.3477263342819679E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="7">
         <v>89.775249121000002</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="7">
         <v>1670.7743951729999</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="7">
         <v>6862.3696171660004</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="10">
         <f t="shared" si="0"/>
         <v>1.1319886387635812E-2</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="10">
         <f t="shared" si="1"/>
         <v>1.995014738990715E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="7">
         <v>0</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="7">
         <v>2122.2444002960001</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="7">
         <v>7003.3199271439998</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="10">
         <f t="shared" si="0"/>
         <v>1.4378701018852701E-2</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="10">
         <f t="shared" si="1"/>
         <v>2.0359915387783586E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49" s="7">
         <v>65.5</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="7">
         <v>813.80705172900002</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="7">
         <v>1219.7231419239999</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="10">
         <f t="shared" si="0"/>
         <v>5.5137326700983261E-3</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="10">
         <f t="shared" si="1"/>
         <v>3.5459553789400334E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50" s="7">
         <v>0</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="7">
         <v>2631.825828735</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="7">
         <v>8480.4302790540005</v>
       </c>
-      <c r="E50" s="16">
+      <c r="E50" s="10">
         <f t="shared" si="0"/>
         <v>1.783123410281905E-2</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="10">
         <f t="shared" si="1"/>
         <v>2.4654141854111987E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="7">
         <f>SUM(B3:B50)</f>
         <v>1713.1821942700003</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="7">
         <f t="shared" ref="C51:D51" si="2">SUM(C3:C50)</f>
         <v>147596.39257492102</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="7">
         <f t="shared" si="2"/>
         <v>343975.88564371696</v>
       </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3172,624 +3141,624 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC1B719-F3CC-8C44-97DC-B36B39C2C0F3}">
   <dimension ref="A1:C52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="3"/>
+    <col min="1" max="2" width="10.85546875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" t="s">
         <v>75</v>
       </c>
       <c r="C1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>2713.1999999999971</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C2" s="10">
         <f>B2/$B$52</f>
         <v>2.5299966197708432E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>29144.499999999985</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="10">
         <f t="shared" ref="C3:C51" si="0">B3/$B$52</f>
         <v>2.7176576177543633E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>14753.5</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="10">
         <f t="shared" si="0"/>
         <v>1.3757299546583066E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>26533.999999999985</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="10">
         <f t="shared" si="0"/>
         <v>2.4742344946557419E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>71322.899999999892</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="10">
         <f t="shared" si="0"/>
         <v>6.6506964437658037E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>16021.799999999988</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="10">
         <f t="shared" si="0"/>
         <v>1.4939960136607883E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>9378.1999999999953</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="10">
         <f t="shared" si="0"/>
         <v>8.7449558821815331E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>3343.4999999999995</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="10">
         <f t="shared" si="0"/>
         <v>3.1177368783000966E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>60433.999999999898</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="10">
         <f t="shared" si="0"/>
         <v>5.6353315538563709E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>34765</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="10">
         <f t="shared" si="0"/>
         <v>3.2417563204457267E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>2873.8999999999901</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="10">
         <f t="shared" si="0"/>
         <v>2.6798456750550675E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>20391.400000000001</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="10">
         <f t="shared" si="0"/>
         <v>1.9014511673446571E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>5211.8999999999969</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="10">
         <f t="shared" si="0"/>
         <v>4.8599769211940379E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>44117.199999999895</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="10">
         <f t="shared" si="0"/>
         <v>4.113827468441475E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>26624.69999999999</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="10">
         <f t="shared" si="0"/>
         <v>2.482692061123869E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>16231.499999999989</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="10">
         <f t="shared" si="0"/>
         <v>1.5135500565314189E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>19495.499999999989</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="10">
         <f t="shared" si="0"/>
         <v>1.8179105521429494E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>24298.6</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="10">
         <f t="shared" si="0"/>
         <v>2.2657885841502239E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>11013.199999999999</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="10">
         <f t="shared" si="0"/>
         <v>1.0269555791265029E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>14601.899999999987</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="10">
         <f t="shared" si="0"/>
         <v>1.3615936032077209E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <v>4739.2999999999956</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="10">
         <f t="shared" si="0"/>
         <v>4.4192882869231757E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <v>26973.899999999976</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="10">
         <f t="shared" si="0"/>
         <v>2.5152541582646602E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <v>17354.099999999995</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="10">
         <f t="shared" si="0"/>
         <v>1.6182299255184E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <v>20394.099999999988</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="10">
         <f t="shared" si="0"/>
         <v>1.9017029361369814E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26">
         <v>14540.79999999999</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="10">
         <f t="shared" si="0"/>
         <v>1.3558961686850911E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27">
         <v>6333.1</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="10">
         <f t="shared" si="0"/>
         <v>5.9054701432517858E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28">
         <v>34773.200000000004</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="10">
         <f t="shared" si="0"/>
         <v>3.2425209515927908E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29">
         <v>8649.6999999999971</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="10">
         <f t="shared" si="0"/>
         <v>8.0656463814064126E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30">
         <v>9465.7999999999884</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="10">
         <f t="shared" si="0"/>
         <v>8.826640868136091E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31">
         <v>4497.2000000000007</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="10">
         <f t="shared" si="0"/>
         <v>4.1935356031377897E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32">
         <v>16796.7</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="10">
         <f t="shared" si="0"/>
         <v>1.5662536570582697E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33">
         <v>8768.0999999999985</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="10">
         <f t="shared" si="0"/>
         <v>8.1760516592262831E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34">
         <v>11931.299999999988</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="10">
         <f t="shared" si="0"/>
         <v>1.112566293287331E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35">
         <v>38881.199999999983</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="10">
         <f t="shared" si="0"/>
         <v>3.6255825067313202E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36">
         <v>28330.599999999977</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="10">
         <f t="shared" si="0"/>
         <v>2.6417633140232887E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37">
         <v>27117.599999999988</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="10">
         <f t="shared" si="0"/>
         <v>2.5286538528784409E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38">
         <v>16782.39999999998</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="10">
         <f t="shared" si="0"/>
         <v>1.5649202149359498E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39">
         <v>46211.599999999911</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="10">
         <f t="shared" si="0"/>
         <v>4.3091254531255417E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40">
         <v>2027.1999999999998</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="10">
         <f t="shared" si="0"/>
         <v>1.8903173918618083E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41">
         <v>21241.9</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="10">
         <f t="shared" si="0"/>
         <v>1.9807583369272571E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42">
         <v>4681.3999999999996</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="10">
         <f t="shared" si="0"/>
         <v>4.3652978681244427E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43">
         <v>19787.399999999991</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="10">
         <f t="shared" si="0"/>
         <v>1.8451295560243851E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>67</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44">
         <v>124983.3</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="10">
         <f t="shared" si="0"/>
         <v>0.1165440537106758</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45">
         <v>8973.2999999999993</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="10">
         <f t="shared" si="0"/>
         <v>8.3673959413938272E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46">
         <v>24707.699999999993</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="10">
         <f t="shared" si="0"/>
         <v>2.3039362185726123E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47">
         <v>795.29999999999905</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="10">
         <f t="shared" si="0"/>
         <v>7.415989649505202E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>71</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48">
         <v>30607.19999999999</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="10">
         <f t="shared" si="0"/>
         <v>2.8540510298042981E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49">
         <v>15311.799999999997</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="10">
         <f t="shared" si="0"/>
         <v>1.4277901460492124E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50">
         <v>14818.199999999999</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="10">
         <f t="shared" si="0"/>
         <v>1.3817630809040376E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>74</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51">
         <v>8666.7000000000007</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="10">
         <f t="shared" si="0"/>
         <v>8.0814984905528495E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B52">
         <f>SUM(B2:B51)</f>
         <v>1072412.4999999991</v>
       </c>
@@ -3802,1886 +3771,1886 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1A0269-252D-274B-A40A-9A6BE88485B6}">
   <dimension ref="A1:AG95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="17"/>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-    </row>
-    <row r="2" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+    <row r="1" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+    </row>
+    <row r="2" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17"/>
-      <c r="W2" s="17"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17"/>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="17"/>
-    </row>
-    <row r="3" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
+    </row>
+    <row r="3" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
-      <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
-      <c r="X3" s="17"/>
-      <c r="Y3" s="17"/>
-      <c r="Z3" s="17"/>
-      <c r="AA3" s="17"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="17"/>
-      <c r="AD3" s="17"/>
-      <c r="AE3" s="17"/>
-      <c r="AF3" s="17"/>
-      <c r="AG3" s="17"/>
-    </row>
-    <row r="4" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11"/>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3" s="11"/>
+      <c r="AF3" s="11"/>
+      <c r="AG3" s="11"/>
+    </row>
+    <row r="4" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="17"/>
-      <c r="AC4" s="17"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="17"/>
-      <c r="AF4" s="17"/>
-      <c r="AG4" s="17"/>
-    </row>
-    <row r="5" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="11"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="11"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="11"/>
+    </row>
+    <row r="5" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="17"/>
-      <c r="AC5" s="17"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="17"/>
-      <c r="AG5" s="17"/>
-    </row>
-    <row r="6" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11"/>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+    </row>
+    <row r="6" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="18" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="17"/>
-      <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="17"/>
-      <c r="AB6" s="17"/>
-      <c r="AC6" s="17"/>
-      <c r="AD6" s="17"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="17"/>
-    </row>
-    <row r="7" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+    </row>
+    <row r="7" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="19">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="13">
         <f>'Gridlab Battery Data (Old)'!B51/1000</f>
         <v>1.7131821942700003</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="11">
         <v>27</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="11">
         <f>F7*1.5</f>
         <v>40.5</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="17"/>
-      <c r="U7" s="17"/>
-      <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="17"/>
-      <c r="Y7" s="17"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="17"/>
-      <c r="AB7" s="17"/>
-      <c r="AC7" s="17"/>
-      <c r="AD7" s="17"/>
-      <c r="AE7" s="17"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="17"/>
-    </row>
-    <row r="8" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-    </row>
-    <row r="9" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="18" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+    </row>
+    <row r="8" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+      <c r="AB8" s="11"/>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="11"/>
+      <c r="AE8" s="11"/>
+      <c r="AF8" s="11"/>
+      <c r="AG8" s="11"/>
+    </row>
+    <row r="9" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-    </row>
-    <row r="10" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17">
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="11"/>
+      <c r="W9" s="11"/>
+      <c r="X9" s="11"/>
+      <c r="Y9" s="11"/>
+      <c r="Z9" s="11"/>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+    </row>
+    <row r="10" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11">
         <f>'Gridlab Battery Data (Old)'!B51/1000</f>
         <v>1.7131821942700003</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="13">
         <f>'Gridlab Battery Data (Old)'!C51/1000 * 1.5</f>
         <v>221.39458886238154</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="13">
         <f>'Gridlab Battery Data (Old)'!D51/1000 * 1.5</f>
         <v>515.96382846557538</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-    </row>
-    <row r="11" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-    </row>
-    <row r="12" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="17"/>
-      <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="17"/>
-      <c r="Y12" s="17"/>
-      <c r="Z12" s="17"/>
-      <c r="AA12" s="17"/>
-      <c r="AB12" s="17"/>
-      <c r="AC12" s="17"/>
-      <c r="AD12" s="17"/>
-      <c r="AE12" s="17"/>
-      <c r="AF12" s="17"/>
-      <c r="AG12" s="17"/>
-    </row>
-    <row r="13" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
-      <c r="AE13" s="17"/>
-      <c r="AF13" s="17"/>
-      <c r="AG13" s="17"/>
-    </row>
-    <row r="14" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="17"/>
-      <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="17"/>
-      <c r="Y14" s="17"/>
-      <c r="Z14" s="17"/>
-      <c r="AA14" s="17"/>
-      <c r="AB14" s="17"/>
-      <c r="AC14" s="17"/>
-      <c r="AD14" s="17"/>
-      <c r="AE14" s="17"/>
-      <c r="AF14" s="17"/>
-      <c r="AG14" s="17"/>
-    </row>
-    <row r="15" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="17"/>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-      <c r="AC15" s="17"/>
-      <c r="AD15" s="17"/>
-      <c r="AE15" s="17"/>
-      <c r="AF15" s="17"/>
-      <c r="AG15" s="17"/>
-    </row>
-    <row r="16" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="17"/>
-      <c r="Y16" s="17"/>
-      <c r="Z16" s="17"/>
-      <c r="AA16" s="17"/>
-      <c r="AB16" s="17"/>
-      <c r="AC16" s="17"/>
-      <c r="AD16" s="17"/>
-      <c r="AE16" s="17"/>
-      <c r="AF16" s="17"/>
-      <c r="AG16" s="17"/>
-    </row>
-    <row r="17" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="17"/>
-      <c r="Y17" s="17"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="17"/>
-      <c r="AB17" s="17"/>
-      <c r="AC17" s="17"/>
-      <c r="AD17" s="17"/>
-      <c r="AE17" s="17"/>
-      <c r="AF17" s="17"/>
-      <c r="AG17" s="17"/>
-    </row>
-    <row r="18" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
-      <c r="AD18" s="17"/>
-      <c r="AE18" s="17"/>
-      <c r="AF18" s="17"/>
-      <c r="AG18" s="17"/>
-    </row>
-    <row r="19" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="17"/>
-    </row>
-    <row r="20" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="17"/>
-      <c r="Y20" s="17"/>
-      <c r="Z20" s="17"/>
-      <c r="AA20" s="17"/>
-      <c r="AB20" s="17"/>
-      <c r="AC20" s="17"/>
-      <c r="AD20" s="17"/>
-      <c r="AE20" s="17"/>
-      <c r="AF20" s="17"/>
-      <c r="AG20" s="17"/>
-    </row>
-    <row r="21" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="17"/>
-      <c r="Y21" s="17"/>
-      <c r="Z21" s="17"/>
-      <c r="AA21" s="17"/>
-      <c r="AB21" s="17"/>
-      <c r="AC21" s="17"/>
-      <c r="AD21" s="17"/>
-      <c r="AE21" s="17"/>
-      <c r="AF21" s="17"/>
-      <c r="AG21" s="17"/>
-    </row>
-    <row r="22" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="17"/>
-      <c r="Y22" s="17"/>
-      <c r="Z22" s="17"/>
-      <c r="AA22" s="17"/>
-      <c r="AB22" s="17"/>
-      <c r="AC22" s="17"/>
-      <c r="AD22" s="17"/>
-      <c r="AE22" s="17"/>
-      <c r="AF22" s="17"/>
-      <c r="AG22" s="17"/>
-    </row>
-    <row r="23" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="17"/>
-      <c r="Y23" s="17"/>
-      <c r="Z23" s="17"/>
-      <c r="AA23" s="17"/>
-      <c r="AB23" s="17"/>
-      <c r="AC23" s="17"/>
-      <c r="AD23" s="17"/>
-      <c r="AE23" s="17"/>
-      <c r="AF23" s="17"/>
-      <c r="AG23" s="17"/>
-    </row>
-    <row r="24" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="17"/>
-      <c r="U24" s="17"/>
-      <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="17"/>
-      <c r="Y24" s="17"/>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-    </row>
-    <row r="25" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="17"/>
-      <c r="U25" s="17"/>
-      <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="17"/>
-      <c r="Y25" s="17"/>
-      <c r="Z25" s="17"/>
-      <c r="AA25" s="17"/>
-      <c r="AB25" s="17"/>
-      <c r="AC25" s="17"/>
-      <c r="AD25" s="17"/>
-      <c r="AE25" s="17"/>
-      <c r="AF25" s="17"/>
-      <c r="AG25" s="17"/>
-    </row>
-    <row r="26" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="17"/>
-      <c r="Y26" s="17"/>
-      <c r="Z26" s="17"/>
-      <c r="AA26" s="17"/>
-      <c r="AB26" s="17"/>
-      <c r="AC26" s="17"/>
-      <c r="AD26" s="17"/>
-      <c r="AE26" s="17"/>
-      <c r="AF26" s="17"/>
-      <c r="AG26" s="17"/>
-    </row>
-    <row r="27" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-      <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="17"/>
-      <c r="Y27" s="17"/>
-      <c r="Z27" s="17"/>
-      <c r="AA27" s="17"/>
-      <c r="AB27" s="17"/>
-      <c r="AC27" s="17"/>
-      <c r="AD27" s="17"/>
-      <c r="AE27" s="17"/>
-      <c r="AF27" s="17"/>
-      <c r="AG27" s="17"/>
-    </row>
-    <row r="28" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="17"/>
-      <c r="U28" s="17"/>
-      <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="17"/>
-      <c r="Z28" s="17"/>
-      <c r="AA28" s="17"/>
-      <c r="AB28" s="17"/>
-      <c r="AC28" s="17"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="17"/>
-      <c r="AF28" s="17"/>
-      <c r="AG28" s="17"/>
-    </row>
-    <row r="29" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="18" t="s">
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="11"/>
+      <c r="X10" s="11"/>
+      <c r="Y10" s="11"/>
+      <c r="Z10" s="11"/>
+      <c r="AA10" s="11"/>
+      <c r="AB10" s="11"/>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="11"/>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="11"/>
+      <c r="AG10" s="11"/>
+    </row>
+    <row r="11" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="11"/>
+      <c r="X11" s="11"/>
+      <c r="Y11" s="11"/>
+      <c r="Z11" s="11"/>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+    </row>
+    <row r="12" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="11"/>
+      <c r="X12" s="11"/>
+      <c r="Y12" s="11"/>
+      <c r="Z12" s="11"/>
+      <c r="AA12" s="11"/>
+      <c r="AB12" s="11"/>
+      <c r="AC12" s="11"/>
+      <c r="AD12" s="11"/>
+      <c r="AE12" s="11"/>
+      <c r="AF12" s="11"/>
+      <c r="AG12" s="11"/>
+    </row>
+    <row r="13" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="11"/>
+      <c r="X13" s="11"/>
+      <c r="Y13" s="11"/>
+      <c r="Z13" s="11"/>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+    </row>
+    <row r="14" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="11"/>
+      <c r="X14" s="11"/>
+      <c r="Y14" s="11"/>
+      <c r="Z14" s="11"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="11"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
+      <c r="AF14" s="11"/>
+      <c r="AG14" s="11"/>
+    </row>
+    <row r="15" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="11"/>
+      <c r="AC15" s="11"/>
+      <c r="AD15" s="11"/>
+      <c r="AE15" s="11"/>
+      <c r="AF15" s="11"/>
+      <c r="AG15" s="11"/>
+    </row>
+    <row r="16" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
+      <c r="AD16" s="11"/>
+      <c r="AE16" s="11"/>
+      <c r="AF16" s="11"/>
+      <c r="AG16" s="11"/>
+    </row>
+    <row r="17" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+      <c r="AB17" s="11"/>
+      <c r="AC17" s="11"/>
+      <c r="AD17" s="11"/>
+      <c r="AE17" s="11"/>
+      <c r="AF17" s="11"/>
+      <c r="AG17" s="11"/>
+    </row>
+    <row r="18" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="11"/>
+      <c r="U18" s="11"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="11"/>
+      <c r="X18" s="11"/>
+      <c r="Y18" s="11"/>
+      <c r="Z18" s="11"/>
+      <c r="AA18" s="11"/>
+      <c r="AB18" s="11"/>
+      <c r="AC18" s="11"/>
+      <c r="AD18" s="11"/>
+      <c r="AE18" s="11"/>
+      <c r="AF18" s="11"/>
+      <c r="AG18" s="11"/>
+    </row>
+    <row r="19" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="11"/>
+      <c r="U19" s="11"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="11"/>
+      <c r="X19" s="11"/>
+      <c r="Y19" s="11"/>
+      <c r="Z19" s="11"/>
+      <c r="AA19" s="11"/>
+      <c r="AB19" s="11"/>
+      <c r="AC19" s="11"/>
+      <c r="AD19" s="11"/>
+      <c r="AE19" s="11"/>
+      <c r="AF19" s="11"/>
+      <c r="AG19" s="11"/>
+    </row>
+    <row r="20" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="11"/>
+      <c r="O20" s="11"/>
+      <c r="P20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+      <c r="S20" s="11"/>
+      <c r="T20" s="11"/>
+      <c r="U20" s="11"/>
+      <c r="V20" s="11"/>
+      <c r="W20" s="11"/>
+      <c r="X20" s="11"/>
+      <c r="Y20" s="11"/>
+      <c r="Z20" s="11"/>
+      <c r="AA20" s="11"/>
+      <c r="AB20" s="11"/>
+      <c r="AC20" s="11"/>
+      <c r="AD20" s="11"/>
+      <c r="AE20" s="11"/>
+      <c r="AF20" s="11"/>
+      <c r="AG20" s="11"/>
+    </row>
+    <row r="21" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+      <c r="S21" s="11"/>
+      <c r="T21" s="11"/>
+      <c r="U21" s="11"/>
+      <c r="V21" s="11"/>
+      <c r="W21" s="11"/>
+      <c r="X21" s="11"/>
+      <c r="Y21" s="11"/>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="11"/>
+      <c r="AD21" s="11"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="11"/>
+      <c r="AG21" s="11"/>
+    </row>
+    <row r="22" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="11"/>
+      <c r="Q22" s="11"/>
+      <c r="R22" s="11"/>
+      <c r="S22" s="11"/>
+      <c r="T22" s="11"/>
+      <c r="U22" s="11"/>
+      <c r="V22" s="11"/>
+      <c r="W22" s="11"/>
+      <c r="X22" s="11"/>
+      <c r="Y22" s="11"/>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="11"/>
+      <c r="AD22" s="11"/>
+      <c r="AE22" s="11"/>
+      <c r="AF22" s="11"/>
+      <c r="AG22" s="11"/>
+    </row>
+    <row r="23" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+      <c r="T23" s="11"/>
+      <c r="U23" s="11"/>
+      <c r="V23" s="11"/>
+      <c r="W23" s="11"/>
+      <c r="X23" s="11"/>
+      <c r="Y23" s="11"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="11"/>
+      <c r="AC23" s="11"/>
+      <c r="AD23" s="11"/>
+      <c r="AE23" s="11"/>
+      <c r="AF23" s="11"/>
+      <c r="AG23" s="11"/>
+    </row>
+    <row r="24" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+      <c r="AB24" s="11"/>
+      <c r="AC24" s="11"/>
+      <c r="AD24" s="11"/>
+      <c r="AE24" s="11"/>
+      <c r="AF24" s="11"/>
+      <c r="AG24" s="11"/>
+    </row>
+    <row r="25" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="11"/>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="11"/>
+    </row>
+    <row r="26" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
+      <c r="AA26" s="11"/>
+      <c r="AB26" s="11"/>
+      <c r="AC26" s="11"/>
+      <c r="AD26" s="11"/>
+      <c r="AE26" s="11"/>
+      <c r="AF26" s="11"/>
+      <c r="AG26" s="11"/>
+    </row>
+    <row r="27" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="11"/>
+      <c r="O27" s="11"/>
+      <c r="P27" s="11"/>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="11"/>
+      <c r="S27" s="11"/>
+      <c r="T27" s="11"/>
+      <c r="U27" s="11"/>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="Z27" s="11"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
+      <c r="AD27" s="11"/>
+      <c r="AE27" s="11"/>
+      <c r="AF27" s="11"/>
+      <c r="AG27" s="11"/>
+    </row>
+    <row r="28" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="11"/>
+      <c r="O28" s="11"/>
+      <c r="P28" s="11"/>
+      <c r="Q28" s="11"/>
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+      <c r="T28" s="11"/>
+      <c r="U28" s="11"/>
+      <c r="V28" s="11"/>
+      <c r="W28" s="11"/>
+      <c r="X28" s="11"/>
+      <c r="Y28" s="11"/>
+      <c r="Z28" s="11"/>
+      <c r="AA28" s="11"/>
+      <c r="AB28" s="11"/>
+      <c r="AC28" s="11"/>
+      <c r="AD28" s="11"/>
+      <c r="AE28" s="11"/>
+      <c r="AF28" s="11"/>
+      <c r="AG28" s="11"/>
+    </row>
+    <row r="29" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="17"/>
-      <c r="U29" s="17"/>
-      <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="17"/>
-      <c r="Y29" s="17"/>
-      <c r="Z29" s="17"/>
-      <c r="AA29" s="17"/>
-      <c r="AB29" s="17"/>
-      <c r="AC29" s="17"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="17"/>
-      <c r="AF29" s="17"/>
-      <c r="AG29" s="17"/>
-    </row>
-    <row r="30" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="str">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="11"/>
+      <c r="O29" s="11"/>
+      <c r="P29" s="11"/>
+      <c r="Q29" s="11"/>
+      <c r="R29" s="11"/>
+      <c r="S29" s="11"/>
+      <c r="T29" s="11"/>
+      <c r="U29" s="11"/>
+      <c r="V29" s="11"/>
+      <c r="W29" s="11"/>
+      <c r="X29" s="11"/>
+      <c r="Y29" s="11"/>
+      <c r="Z29" s="11"/>
+      <c r="AA29" s="11"/>
+      <c r="AB29" s="11"/>
+      <c r="AC29" s="11"/>
+      <c r="AD29" s="11"/>
+      <c r="AE29" s="11"/>
+      <c r="AF29" s="11"/>
+      <c r="AG29" s="11"/>
+    </row>
+    <row r="30" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="str">
         <f>About!B2</f>
         <v>KY</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="17"/>
-      <c r="U30" s="17"/>
-      <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="17"/>
-      <c r="Y30" s="17"/>
-      <c r="Z30" s="17"/>
-      <c r="AA30" s="17"/>
-      <c r="AB30" s="17"/>
-      <c r="AC30" s="17"/>
-      <c r="AD30" s="17"/>
-      <c r="AE30" s="17"/>
-      <c r="AF30" s="17"/>
-      <c r="AG30" s="17"/>
-    </row>
-    <row r="31" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="20">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="P30" s="11"/>
+      <c r="Q30" s="11"/>
+      <c r="R30" s="11"/>
+      <c r="S30" s="11"/>
+      <c r="T30" s="11"/>
+      <c r="U30" s="11"/>
+      <c r="V30" s="11"/>
+      <c r="W30" s="11"/>
+      <c r="X30" s="11"/>
+      <c r="Y30" s="11"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="11"/>
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="11"/>
+      <c r="AD30" s="11"/>
+      <c r="AE30" s="11"/>
+      <c r="AF30" s="11"/>
+      <c r="AG30" s="11"/>
+    </row>
+    <row r="31" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="14">
         <v>2019</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="12">
         <v>2035</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="12">
         <v>2050</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="17"/>
-      <c r="U31" s="17"/>
-      <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="17"/>
-      <c r="Y31" s="17"/>
-      <c r="Z31" s="17"/>
-      <c r="AA31" s="17"/>
-      <c r="AB31" s="17"/>
-      <c r="AC31" s="17"/>
-      <c r="AD31" s="17"/>
-      <c r="AE31" s="17"/>
-      <c r="AF31" s="17"/>
-      <c r="AG31" s="17"/>
-    </row>
-    <row r="32" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="s">
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="11"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="11"/>
+      <c r="V31" s="11"/>
+      <c r="W31" s="11"/>
+      <c r="X31" s="11"/>
+      <c r="Y31" s="11"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="11"/>
+      <c r="AC31" s="11"/>
+      <c r="AD31" s="11"/>
+      <c r="AE31" s="11"/>
+      <c r="AF31" s="11"/>
+      <c r="AG31" s="11"/>
+    </row>
+    <row r="32" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="17">
+      <c r="B32" s="15"/>
+      <c r="C32" s="11">
         <f>SUMIFS('SYC 2019'!C2:C51,'SYC 2019'!A2:A51,Calculations!A30)</f>
         <v>1.8179105521429494E-2</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="11">
         <f>C32</f>
         <v>1.8179105521429494E-2</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="17"/>
-      <c r="Y32" s="17"/>
-      <c r="Z32" s="17"/>
-      <c r="AA32" s="17"/>
-      <c r="AB32" s="17"/>
-      <c r="AC32" s="17"/>
-      <c r="AD32" s="17"/>
-      <c r="AE32" s="17"/>
-      <c r="AF32" s="17"/>
-      <c r="AG32" s="17"/>
-    </row>
-    <row r="33" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="11"/>
+      <c r="Q32" s="11"/>
+      <c r="R32" s="11"/>
+      <c r="S32" s="11"/>
+      <c r="T32" s="11"/>
+      <c r="U32" s="11"/>
+      <c r="V32" s="11"/>
+      <c r="W32" s="11"/>
+      <c r="X32" s="11"/>
+      <c r="Y32" s="11"/>
+      <c r="Z32" s="11"/>
+      <c r="AA32" s="11"/>
+      <c r="AB32" s="11"/>
+      <c r="AC32" s="11"/>
+      <c r="AD32" s="11"/>
+      <c r="AE32" s="11"/>
+      <c r="AF32" s="11"/>
+      <c r="AG32" s="11"/>
+    </row>
+    <row r="33" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="21">
+      <c r="B33" s="15">
         <f>SUMIFS('Gridlab Battery Data (Old)'!B3:B51,'Gridlab Battery Data (Old)'!A3:A51,Calculations!A30)</f>
         <v>0</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="11">
         <f>C32*F7*1000</f>
         <v>490.83584907859637</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="11">
         <f>D32*G7*1000</f>
         <v>736.25377361789458</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="17"/>
-      <c r="AB33" s="17"/>
-      <c r="AC33" s="17"/>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="17"/>
-    </row>
-    <row r="34" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="11"/>
+      <c r="P33" s="11"/>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11"/>
+      <c r="S33" s="11"/>
+      <c r="T33" s="11"/>
+      <c r="U33" s="11"/>
+      <c r="V33" s="11"/>
+      <c r="W33" s="11"/>
+      <c r="X33" s="11"/>
+      <c r="Y33" s="11"/>
+      <c r="Z33" s="11"/>
+      <c r="AA33" s="11"/>
+      <c r="AB33" s="11"/>
+      <c r="AC33" s="11"/>
+      <c r="AD33" s="11"/>
+      <c r="AE33" s="11"/>
+      <c r="AF33" s="11"/>
+      <c r="AG33" s="11"/>
+    </row>
+    <row r="34" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="15">
         <f>B33</f>
         <v>0</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="11">
         <f>C32*F10*1000</f>
         <v>4024.7555928027332</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="11">
         <f>D32*G10*1000</f>
         <v>9379.7608829164419</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="17"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="17"/>
-      <c r="AF34" s="17"/>
-      <c r="AG34" s="17"/>
-    </row>
-    <row r="35" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-    </row>
-    <row r="36" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="17"/>
-      <c r="B36" s="20">
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="11"/>
+      <c r="P34" s="11"/>
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11"/>
+      <c r="S34" s="11"/>
+      <c r="T34" s="11"/>
+      <c r="U34" s="11"/>
+      <c r="V34" s="11"/>
+      <c r="W34" s="11"/>
+      <c r="X34" s="11"/>
+      <c r="Y34" s="11"/>
+      <c r="Z34" s="11"/>
+      <c r="AA34" s="11"/>
+      <c r="AB34" s="11"/>
+      <c r="AC34" s="11"/>
+      <c r="AD34" s="11"/>
+      <c r="AE34" s="11"/>
+      <c r="AF34" s="11"/>
+      <c r="AG34" s="11"/>
+    </row>
+    <row r="35" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+      <c r="U35" s="11"/>
+      <c r="V35" s="11"/>
+      <c r="W35" s="11"/>
+      <c r="X35" s="11"/>
+      <c r="Y35" s="11"/>
+      <c r="Z35" s="11"/>
+      <c r="AA35" s="11"/>
+      <c r="AB35" s="11"/>
+      <c r="AC35" s="11"/>
+      <c r="AD35" s="11"/>
+      <c r="AE35" s="11"/>
+      <c r="AF35" s="11"/>
+      <c r="AG35" s="11"/>
+    </row>
+    <row r="36" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="14">
         <v>2019</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="12">
         <f t="shared" ref="C36:AG36" si="0">B36+1</f>
         <v>2020</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="12">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="12">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="F36" s="18">
+      <c r="F36" s="12">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="12">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="H36" s="18">
+      <c r="H36" s="12">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="12">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="J36" s="18">
+      <c r="J36" s="12">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="K36" s="18">
+      <c r="K36" s="12">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="L36" s="18">
+      <c r="L36" s="12">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="N36" s="18">
+      <c r="N36" s="12">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="O36" s="18">
+      <c r="O36" s="12">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="P36" s="18">
+      <c r="P36" s="12">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="Q36" s="18">
+      <c r="Q36" s="12">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="R36" s="20">
+      <c r="R36" s="14">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
-      <c r="S36" s="18">
+      <c r="S36" s="12">
         <f t="shared" si="0"/>
         <v>2036</v>
       </c>
-      <c r="T36" s="18">
+      <c r="T36" s="12">
         <f t="shared" si="0"/>
         <v>2037</v>
       </c>
-      <c r="U36" s="18">
+      <c r="U36" s="12">
         <f t="shared" si="0"/>
         <v>2038</v>
       </c>
-      <c r="V36" s="18">
+      <c r="V36" s="12">
         <f t="shared" si="0"/>
         <v>2039</v>
       </c>
-      <c r="W36" s="18">
+      <c r="W36" s="12">
         <f t="shared" si="0"/>
         <v>2040</v>
       </c>
-      <c r="X36" s="18">
+      <c r="X36" s="12">
         <f t="shared" si="0"/>
         <v>2041</v>
       </c>
-      <c r="Y36" s="18">
+      <c r="Y36" s="12">
         <f t="shared" si="0"/>
         <v>2042</v>
       </c>
-      <c r="Z36" s="18">
+      <c r="Z36" s="12">
         <f t="shared" si="0"/>
         <v>2043</v>
       </c>
-      <c r="AA36" s="18">
+      <c r="AA36" s="12">
         <f t="shared" si="0"/>
         <v>2044</v>
       </c>
-      <c r="AB36" s="18">
+      <c r="AB36" s="12">
         <f t="shared" si="0"/>
         <v>2045</v>
       </c>
-      <c r="AC36" s="18">
+      <c r="AC36" s="12">
         <f t="shared" si="0"/>
         <v>2046</v>
       </c>
-      <c r="AD36" s="18">
+      <c r="AD36" s="12">
         <f t="shared" si="0"/>
         <v>2047</v>
       </c>
-      <c r="AE36" s="18">
+      <c r="AE36" s="12">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="AF36" s="18">
+      <c r="AF36" s="12">
         <f t="shared" si="0"/>
         <v>2049</v>
       </c>
-      <c r="AG36" s="20">
+      <c r="AG36" s="14">
         <f t="shared" si="0"/>
         <v>2050</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="17" t="s">
+    <row r="37" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="15">
         <f>B34</f>
         <v>0</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="11">
         <f t="shared" ref="C37:Q37" si="1">($R37-$B37)/($R36-$B36)+B37</f>
         <v>30.677240567412273</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="11">
         <f t="shared" si="1"/>
         <v>61.354481134824546</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="11">
         <f t="shared" si="1"/>
         <v>92.031721702236823</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="11">
         <f t="shared" si="1"/>
         <v>122.70896226964909</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="11">
         <f t="shared" si="1"/>
         <v>153.38620283706138</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="11">
         <f t="shared" si="1"/>
         <v>184.06344340447365</v>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="11">
         <f t="shared" si="1"/>
         <v>214.74068397188591</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="11">
         <f t="shared" si="1"/>
         <v>245.41792453929818</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K37" s="11">
         <f t="shared" si="1"/>
         <v>276.09516510671045</v>
       </c>
-      <c r="L37" s="17">
+      <c r="L37" s="11">
         <f t="shared" si="1"/>
         <v>306.77240567412275</v>
       </c>
-      <c r="M37" s="17">
+      <c r="M37" s="11">
         <f t="shared" si="1"/>
         <v>337.44964624153505</v>
       </c>
-      <c r="N37" s="17">
+      <c r="N37" s="11">
         <f t="shared" si="1"/>
         <v>368.12688680894735</v>
       </c>
-      <c r="O37" s="17">
+      <c r="O37" s="11">
         <f t="shared" si="1"/>
         <v>398.80412737635965</v>
       </c>
-      <c r="P37" s="17">
+      <c r="P37" s="11">
         <f t="shared" si="1"/>
         <v>429.48136794377194</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="11">
         <f t="shared" si="1"/>
         <v>460.15860851118424</v>
       </c>
-      <c r="R37" s="21">
+      <c r="R37" s="15">
         <f>C33</f>
         <v>490.83584907859637</v>
       </c>
-      <c r="S37" s="17">
+      <c r="S37" s="11">
         <f t="shared" ref="S37:AF37" si="2">($AG37-$R37)/($AG36-$R36)+R37</f>
         <v>507.19704404788291</v>
       </c>
-      <c r="T37" s="17">
+      <c r="T37" s="11">
         <f t="shared" si="2"/>
         <v>523.55823901716951</v>
       </c>
-      <c r="U37" s="17">
+      <c r="U37" s="11">
         <f t="shared" si="2"/>
         <v>539.91943398645606</v>
       </c>
-      <c r="V37" s="17">
+      <c r="V37" s="11">
         <f t="shared" si="2"/>
         <v>556.2806289557426</v>
       </c>
-      <c r="W37" s="17">
+      <c r="W37" s="11">
         <f t="shared" si="2"/>
         <v>572.64182392502914</v>
       </c>
-      <c r="X37" s="17">
+      <c r="X37" s="11">
         <f t="shared" si="2"/>
         <v>589.00301889431569</v>
       </c>
-      <c r="Y37" s="17">
+      <c r="Y37" s="11">
         <f t="shared" si="2"/>
         <v>605.36421386360223</v>
       </c>
-      <c r="Z37" s="17">
+      <c r="Z37" s="11">
         <f t="shared" si="2"/>
         <v>621.72540883288877</v>
       </c>
-      <c r="AA37" s="17">
+      <c r="AA37" s="11">
         <f t="shared" si="2"/>
         <v>638.08660380217532</v>
       </c>
-      <c r="AB37" s="17">
+      <c r="AB37" s="11">
         <f t="shared" si="2"/>
         <v>654.44779877146186</v>
       </c>
-      <c r="AC37" s="17">
+      <c r="AC37" s="11">
         <f t="shared" si="2"/>
         <v>670.80899374074841</v>
       </c>
-      <c r="AD37" s="17">
+      <c r="AD37" s="11">
         <f t="shared" si="2"/>
         <v>687.17018871003495</v>
       </c>
-      <c r="AE37" s="17">
+      <c r="AE37" s="11">
         <f t="shared" si="2"/>
         <v>703.53138367932149</v>
       </c>
-      <c r="AF37" s="17">
+      <c r="AF37" s="11">
         <f t="shared" si="2"/>
         <v>719.89257864860804</v>
       </c>
-      <c r="AG37" s="21">
+      <c r="AG37" s="15">
         <f>D33</f>
         <v>736.25377361789458</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="17"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="21"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17"/>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17"/>
-      <c r="Z38" s="17"/>
-      <c r="AA38" s="17"/>
-      <c r="AB38" s="17"/>
-      <c r="AC38" s="17"/>
-      <c r="AD38" s="17"/>
-      <c r="AE38" s="17"/>
-      <c r="AF38" s="17"/>
-      <c r="AG38" s="21"/>
-    </row>
-    <row r="39" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="20">
+    <row r="38" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="11"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="P38" s="11"/>
+      <c r="Q38" s="11"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="11"/>
+      <c r="T38" s="11"/>
+      <c r="U38" s="11"/>
+      <c r="V38" s="11"/>
+      <c r="W38" s="11"/>
+      <c r="X38" s="11"/>
+      <c r="Y38" s="11"/>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="11"/>
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="11"/>
+      <c r="AD38" s="11"/>
+      <c r="AE38" s="11"/>
+      <c r="AF38" s="11"/>
+      <c r="AG38" s="15"/>
+    </row>
+    <row r="39" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="11"/>
+      <c r="B39" s="14">
         <v>2019</v>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="12">
         <f t="shared" ref="C39:AG39" si="3">B39+1</f>
         <v>2020</v>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="12">
         <f t="shared" si="3"/>
         <v>2021</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="12">
         <f t="shared" si="3"/>
         <v>2022</v>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="12">
         <f t="shared" si="3"/>
         <v>2023</v>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="12">
         <f t="shared" si="3"/>
         <v>2024</v>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="12">
         <f t="shared" si="3"/>
         <v>2025</v>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="12">
         <f t="shared" si="3"/>
         <v>2026</v>
       </c>
-      <c r="J39" s="18">
+      <c r="J39" s="12">
         <f t="shared" si="3"/>
         <v>2027</v>
       </c>
-      <c r="K39" s="18">
+      <c r="K39" s="12">
         <f t="shared" si="3"/>
         <v>2028</v>
       </c>
-      <c r="L39" s="18">
+      <c r="L39" s="12">
         <f t="shared" si="3"/>
         <v>2029</v>
       </c>
-      <c r="M39" s="18">
+      <c r="M39" s="12">
         <f t="shared" si="3"/>
         <v>2030</v>
       </c>
-      <c r="N39" s="18">
+      <c r="N39" s="12">
         <f t="shared" si="3"/>
         <v>2031</v>
       </c>
-      <c r="O39" s="18">
+      <c r="O39" s="12">
         <f t="shared" si="3"/>
         <v>2032</v>
       </c>
-      <c r="P39" s="18">
+      <c r="P39" s="12">
         <f t="shared" si="3"/>
         <v>2033</v>
       </c>
-      <c r="Q39" s="18">
+      <c r="Q39" s="12">
         <f t="shared" si="3"/>
         <v>2034</v>
       </c>
-      <c r="R39" s="20">
+      <c r="R39" s="14">
         <f t="shared" si="3"/>
         <v>2035</v>
       </c>
-      <c r="S39" s="18">
+      <c r="S39" s="12">
         <f t="shared" si="3"/>
         <v>2036</v>
       </c>
-      <c r="T39" s="18">
+      <c r="T39" s="12">
         <f t="shared" si="3"/>
         <v>2037</v>
       </c>
-      <c r="U39" s="18">
+      <c r="U39" s="12">
         <f t="shared" si="3"/>
         <v>2038</v>
       </c>
-      <c r="V39" s="18">
+      <c r="V39" s="12">
         <f t="shared" si="3"/>
         <v>2039</v>
       </c>
-      <c r="W39" s="18">
+      <c r="W39" s="12">
         <f t="shared" si="3"/>
         <v>2040</v>
       </c>
-      <c r="X39" s="18">
+      <c r="X39" s="12">
         <f t="shared" si="3"/>
         <v>2041</v>
       </c>
-      <c r="Y39" s="18">
+      <c r="Y39" s="12">
         <f t="shared" si="3"/>
         <v>2042</v>
       </c>
-      <c r="Z39" s="18">
+      <c r="Z39" s="12">
         <f t="shared" si="3"/>
         <v>2043</v>
       </c>
-      <c r="AA39" s="18">
+      <c r="AA39" s="12">
         <f t="shared" si="3"/>
         <v>2044</v>
       </c>
-      <c r="AB39" s="18">
+      <c r="AB39" s="12">
         <f t="shared" si="3"/>
         <v>2045</v>
       </c>
-      <c r="AC39" s="18">
+      <c r="AC39" s="12">
         <f t="shared" si="3"/>
         <v>2046</v>
       </c>
-      <c r="AD39" s="18">
+      <c r="AD39" s="12">
         <f t="shared" si="3"/>
         <v>2047</v>
       </c>
-      <c r="AE39" s="18">
+      <c r="AE39" s="12">
         <f t="shared" si="3"/>
         <v>2048</v>
       </c>
-      <c r="AF39" s="18">
+      <c r="AF39" s="12">
         <f t="shared" si="3"/>
         <v>2049</v>
       </c>
-      <c r="AG39" s="20">
+      <c r="AG39" s="14">
         <f t="shared" si="3"/>
         <v>2050</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
+    <row r="40" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="15">
         <f>B33</f>
         <v>0</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="11">
         <f t="shared" ref="C40:Q40" si="4">($R40-$B40)/($R39-$B39)+B40</f>
         <v>285.55256753053982</v>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="11">
         <f t="shared" si="4"/>
         <v>571.10513506107964</v>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="11">
         <f t="shared" si="4"/>
         <v>856.65770259161945</v>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="11">
         <f t="shared" si="4"/>
         <v>1142.2102701221593</v>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="11">
         <f t="shared" si="4"/>
         <v>1427.7628376526991</v>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="11">
         <f t="shared" si="4"/>
         <v>1713.3154051832389</v>
       </c>
-      <c r="I40" s="17">
+      <c r="I40" s="11">
         <f t="shared" si="4"/>
         <v>1998.8679727137787</v>
       </c>
-      <c r="J40" s="17">
+      <c r="J40" s="11">
         <f t="shared" si="4"/>
         <v>2284.4205402443185</v>
       </c>
-      <c r="K40" s="17">
+      <c r="K40" s="11">
         <f t="shared" si="4"/>
         <v>2569.9731077748584</v>
       </c>
-      <c r="L40" s="17">
+      <c r="L40" s="11">
         <f t="shared" si="4"/>
         <v>2855.5256753053982</v>
       </c>
-      <c r="M40" s="17">
+      <c r="M40" s="11">
         <f t="shared" si="4"/>
         <v>3141.078242835938</v>
       </c>
-      <c r="N40" s="17">
+      <c r="N40" s="11">
         <f t="shared" si="4"/>
         <v>3426.6308103664778</v>
       </c>
-      <c r="O40" s="17">
+      <c r="O40" s="11">
         <f t="shared" si="4"/>
         <v>3712.1833778970176</v>
       </c>
-      <c r="P40" s="17">
+      <c r="P40" s="11">
         <f t="shared" si="4"/>
         <v>3997.7359454275575</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="Q40" s="11">
         <f t="shared" si="4"/>
         <v>4283.2885129580973</v>
       </c>
-      <c r="R40" s="21">
+      <c r="R40" s="15">
         <f>FORECAST(R36,$B$34:$D$34,$B$31:$D$31)</f>
         <v>4568.8410804886371</v>
       </c>
-      <c r="S40" s="17">
+      <c r="S40" s="11">
         <f t="shared" ref="S40:AF40" si="5">($AG40-$R40)/($AG39-$R39)+R40</f>
         <v>4870.8478462354897</v>
       </c>
-      <c r="T40" s="17">
+      <c r="T40" s="11">
         <f t="shared" si="5"/>
         <v>5172.8546119823422</v>
       </c>
-      <c r="U40" s="17">
+      <c r="U40" s="11">
         <f t="shared" si="5"/>
         <v>5474.8613777291948</v>
       </c>
-      <c r="V40" s="17">
+      <c r="V40" s="11">
         <f t="shared" si="5"/>
         <v>5776.8681434760474</v>
       </c>
-      <c r="W40" s="17">
+      <c r="W40" s="11">
         <f t="shared" si="5"/>
         <v>6078.8749092229</v>
       </c>
-      <c r="X40" s="17">
+      <c r="X40" s="11">
         <f t="shared" si="5"/>
         <v>6380.8816749697526</v>
       </c>
-      <c r="Y40" s="17">
+      <c r="Y40" s="11">
         <f t="shared" si="5"/>
         <v>6682.8884407166051</v>
       </c>
-      <c r="Z40" s="17">
+      <c r="Z40" s="11">
         <f t="shared" si="5"/>
         <v>6984.8952064634577</v>
       </c>
-      <c r="AA40" s="17">
+      <c r="AA40" s="11">
         <f t="shared" si="5"/>
         <v>7286.9019722103103</v>
       </c>
-      <c r="AB40" s="17">
+      <c r="AB40" s="11">
         <f t="shared" si="5"/>
         <v>7588.9087379571629</v>
       </c>
-      <c r="AC40" s="17">
+      <c r="AC40" s="11">
         <f t="shared" si="5"/>
         <v>7890.9155037040155</v>
       </c>
-      <c r="AD40" s="17">
+      <c r="AD40" s="11">
         <f t="shared" si="5"/>
         <v>8192.922269450868</v>
       </c>
-      <c r="AE40" s="17">
+      <c r="AE40" s="11">
         <f t="shared" si="5"/>
         <v>8494.9290351977215</v>
       </c>
-      <c r="AF40" s="17">
+      <c r="AF40" s="11">
         <f t="shared" si="5"/>
         <v>8796.935800944575</v>
       </c>
-      <c r="AG40" s="21">
+      <c r="AG40" s="15">
         <f>FORECAST(AG36,$B$34:$D$34,$B$31:$D$31)</f>
         <v>9098.9425666914321</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>86</v>
       </c>
@@ -5695,8 +5664,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A46" s="22" t="s">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
         <v>27</v>
       </c>
       <c r="B46">
@@ -5712,835 +5681,835 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A47" s="22" t="s">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A47)*$G$7*1000</f>
         <v>0</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A47)*$G$10*1000</f>
         <v>0</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A47),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A48" s="22" t="s">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A48)*$G$7*1000</f>
         <v>907.65806391110857</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A48)*$G$10*1000</f>
         <v>11563.425422054999</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A48),2)</f>
         <v>78.3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="22" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A49)*$G$7*1000</f>
         <v>443.26332163270365</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A49)*$G$10*1000</f>
         <v>5647.1071715549997</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A49),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="22" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A50)*$G$7*1000</f>
         <v>2573.9390787312468</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A50)*$G$10*1000</f>
         <v>32791.591637020494</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A50),2)</f>
         <v>444.98</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="22" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A51)*$G$7*1000</f>
         <v>643.47705492620048</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A51)*$G$10*1000</f>
         <v>8197.7996244314982</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A51),2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="22" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A52)*$G$7*1000</f>
         <v>82.643363333980716</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A52)*$G$10*1000</f>
         <v>1052.8638553845001</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A52),2)</f>
         <v>1.6</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="22" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A53)*$G$7*1000</f>
         <v>155.21025775699076</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A53)*$G$10*1000</f>
         <v>1977.3550323314994</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A53),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="22" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A54)*$G$7*1000</f>
         <v>1896.649367609471</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A54)*$G$10*1000</f>
         <v>24163.023925150497</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A54),2)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="22" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A55)*$G$7*1000</f>
         <v>1556.1825007261668</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A55)*$G$10*1000</f>
         <v>19825.527922612499</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A55),2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="22" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A56)*$G$7*1000</f>
         <v>0</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A56)*$G$10*1000</f>
         <v>0</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A56),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="22" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A57)*$G$7*1000</f>
         <v>1011.1791770933995</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A57)*$G$10*1000</f>
         <v>12882.268629081</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A57),2)</f>
         <v>3.09</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="22" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A58)*$G$7*1000</f>
         <v>1401.7883312677982</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A58)*$G$10*1000</f>
         <v>17858.569730846997</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A58),2)</f>
         <v>112.4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="22" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A59)*$G$7*1000</f>
         <v>1686.2356218380089</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A59)*$G$10*1000</f>
         <v>21482.384867618995</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A59),2)</f>
         <v>23</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="22" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A60)*$G$7*1000</f>
         <v>1230.6757025988381</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A60)*$G$10*1000</f>
         <v>15678.620916356998</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A60),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="22" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A61)*$G$7*1000</f>
         <v>194.04156876222194</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A61)*$G$10*1000</f>
         <v>2472.0600172844997</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A61),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="22" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A62)*$G$7*1000</f>
         <v>1330.5983597819095</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A62)*$G$10*1000</f>
         <v>16951.620342298498</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A62),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="22" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A63)*$G$7*1000</f>
         <v>953.59202584536467</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A63)*$G$10*1000</f>
         <v>12148.617097516499</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A63),2)</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="22" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A64)*$G$7*1000</f>
         <v>19.415843565304563</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A64)*$G$10*1000</f>
         <v>247.35488836649998</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A64),2)</f>
         <v>16.2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="22" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A65)*$G$7*1000</f>
         <v>1053.041757106957</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A65)*$G$10*1000</f>
         <v>13415.591519284495</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A65),2)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="22" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A66)*$G$7*1000</f>
         <v>395.7712117344646</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A66)*$G$10*1000</f>
         <v>5042.0649284684996</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A66),2)</f>
         <v>29.5</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="22" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A67)*$G$7*1000</f>
         <v>1298.8557712660281</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A67)*$G$10*1000</f>
         <v>16547.224601654998</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A67),2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="22" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A68)*$G$7*1000</f>
         <v>456.16536000539725</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A68)*$G$10*1000</f>
         <v>5811.4771743644988</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A68),2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="22" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A69)*$G$7*1000</f>
         <v>563.9790921746262</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A69)*$G$10*1000</f>
         <v>7185.0076931594995</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A69),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="22" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A70)*$G$7*1000</f>
         <v>1007.4959002972572</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A70)*$G$10*1000</f>
         <v>12835.344243968999</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A70),2)</f>
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="22" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A71)*$G$7*1000</f>
         <v>333.9942684579799</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A71)*$G$10*1000</f>
         <v>4255.0360849169992</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A71),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="22" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A72)*$G$7*1000</f>
         <v>141.94100873281616</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A72)*$G$10*1000</f>
         <v>1808.3068217789996</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A72),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="22" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A73)*$G$7*1000</f>
         <v>380.23377895103334</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A73)*$G$10*1000</f>
         <v>4844.1204024569988</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A73),2)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="22" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A74)*$G$7*1000</f>
         <v>76.786155272344018</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A74)*$G$10*1000</f>
         <v>978.24391722149983</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A74),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="22" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A75)*$G$7*1000</f>
         <v>235.48162351095189</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A75)*$G$10*1000</f>
         <v>2999.9999999999995</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A75),2)</f>
         <v>320.8</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="22" t="s">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A76)*$G$7*1000</f>
         <v>451.64099798691859</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A76)*$G$10*1000</f>
         <v>5753.8374916874991</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A76),2)</f>
         <v>3.6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="22" t="s">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A77)*$G$7*1000</f>
         <v>649.40414423467803</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A77)*$G$10*1000</f>
         <v>8273.3098390304986</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A77),2)</f>
         <v>254</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="22" t="s">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A78)*$G$7*1000</f>
         <v>2088.8974619505761</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A78)*$G$10*1000</f>
         <v>26612.235351605996</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A78),2)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="22" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A79)*$G$7*1000</f>
         <v>78.985659323150202</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A79)*$G$10*1000</f>
         <v>1006.2652636604998</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A79),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="22" t="s">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A80)*$G$7*1000</f>
         <v>2037.8761861162782</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A80)*$G$10*1000</f>
         <v>25962.232072280996</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A80),2)</f>
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="22" t="s">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A81)*$G$7*1000</f>
         <v>621.52644475165141</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A81)*$G$10*1000</f>
         <v>7918.1521957199993</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A81),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="22" t="s">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A82)*$G$7*1000</f>
         <v>584.20005007259886</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A82)*$G$10*1000</f>
         <v>7442.6196154379995</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A82),2)</f>
         <v>30.14</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="22" t="s">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A83)*$G$7*1000</f>
         <v>734.79882317025078</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A83)*$G$10*1000</f>
         <v>9361.2250359239988</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A83),2)</f>
         <v>30.4</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="22" t="s">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A84)*$G$7*1000</f>
         <v>93.879027867938987</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A84)*$G$10*1000</f>
         <v>1196.0045094165</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A84),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="22" t="s">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A85)*$G$7*1000</f>
         <v>1357.0293994415704</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A85)*$G$10*1000</f>
         <v>17288.347759906497</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A85),2)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="22" t="s">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A86)*$G$7*1000</f>
         <v>161.32636846030783</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A86)*$G$10*1000</f>
         <v>2055.2733506969994</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A86),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="22" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A87)*$G$7*1000</f>
         <v>504.16433045196572</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A87)*$G$10*1000</f>
         <v>6422.9767435994991</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A87),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="22" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A88)*$G$7*1000</f>
         <v>4414.0832227364426</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A88)*$G$10*1000</f>
         <v>56234.747623919997</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A88),2)</f>
         <v>105.2</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="22" t="s">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A89)*$G$7*1000</f>
         <v>123.63174256148407</v>
       </c>
-      <c r="C89" s="3">
+      <c r="C89">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A89)*$G$10*1000</f>
         <v>1575.0495607874998</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A89),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="22" t="s">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A90)*$G$7*1000</f>
         <v>5.4582916538419699</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A90)*$G$10*1000</f>
         <v>69.537803915999987</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A90),2)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="22" t="s">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A91)*$G$7*1000</f>
         <v>704.49340349121462</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A91)*$G$10*1000</f>
         <v>8975.1386072609985</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A91),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="22" t="s">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A92)*$G$7*1000</f>
         <v>807.98096929123949</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A92)*$G$10*1000</f>
         <v>10293.554425748998</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A92),2)</f>
         <v>89.78</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="22" t="s">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A93)*$G$7*1000</f>
         <v>143.61119284707135</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A93)*$G$10*1000</f>
         <v>1829.5847128859996</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A93),2)</f>
         <v>65.5</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="22" t="s">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A94)*$G$7*1000</f>
         <v>824.57657320523526</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A94)*$G$10*1000</f>
         <v>10504.979890715998</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A94),2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="22" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A95)*$G$7*1000</f>
         <v>998.49274509153554</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95">
         <f>SUMIFS('Gridlab Battery Data (Old)'!$F$3:$F$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A95)*$G$10*1000</f>
         <v>12720.645418581</v>
       </c>
-      <c r="D95" s="3">
+      <c r="D95">
         <f>ROUND(SUMIFS('Gridlab Battery Data (Old)'!$B$3:$B$51,'Gridlab Battery Data (Old)'!$A$3:$A$51,Calculations!A95),2)</f>
         <v>0</v>
       </c>
@@ -6553,196 +6522,185 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AG21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AG20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2" s="3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2">
         <v>2019</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2">
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>1000</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>100000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="10"/>
-    </row>
-    <row r="12" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
-    </row>
-    <row r="13" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-    </row>
-    <row r="15" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-    </row>
-    <row r="16" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="10"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="10"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
-    </row>
-    <row r="18" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
-      <c r="AB18" s="9"/>
-      <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="9"/>
-      <c r="AF18" s="9"/>
-      <c r="AG18" s="9"/>
-    </row>
-    <row r="19" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="9"/>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="9"/>
-      <c r="AE19" s="9"/>
-      <c r="AF19" s="9"/>
-      <c r="AG19" s="9"/>
-    </row>
-    <row r="20" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
-      <c r="T20" s="9"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="9"/>
-      <c r="AG20" s="9"/>
-    </row>
-    <row r="21" spans="2:33" s="8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
+      <c r="AD18" s="7"/>
+      <c r="AE18" s="7"/>
+      <c r="AF18" s="7"/>
+      <c r="AG18" s="7"/>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="7"/>
+      <c r="AB19" s="7"/>
+      <c r="AC19" s="7"/>
+      <c r="AD19" s="7"/>
+      <c r="AE19" s="7"/>
+      <c r="AF19" s="7"/>
+      <c r="AG19" s="7"/>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7"/>
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7"/>
+      <c r="Z20" s="7"/>
+      <c r="AA20" s="7"/>
+      <c r="AB20" s="7"/>
+      <c r="AC20" s="7"/>
+      <c r="AD20" s="7"/>
+      <c r="AE20" s="7"/>
+      <c r="AF20" s="7"/>
+      <c r="AG20" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6754,14 +6712,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B1">
@@ -6861,135 +6819,135 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <f>Calculations!B37</f>
         <v>0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <f>Calculations!C37</f>
         <v>30.677240567412273</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <f>Calculations!D37</f>
         <v>61.354481134824546</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>Calculations!E37</f>
         <v>92.031721702236823</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <f>Calculations!F37</f>
         <v>122.70896226964909</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <f>Calculations!G37</f>
         <v>153.38620283706138</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <f>Calculations!H37</f>
         <v>184.06344340447365</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <f>Calculations!I37</f>
         <v>214.74068397188591</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <f>Calculations!J37</f>
         <v>245.41792453929818</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <f>Calculations!K37</f>
         <v>276.09516510671045</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <f>Calculations!L37</f>
         <v>306.77240567412275</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <f>Calculations!M37</f>
         <v>337.44964624153505</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <f>Calculations!N37</f>
         <v>368.12688680894735</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <f>Calculations!O37</f>
         <v>398.80412737635965</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <f>Calculations!P37</f>
         <v>429.48136794377194</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <f>Calculations!Q37</f>
         <v>460.15860851118424</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <f>Calculations!R37</f>
         <v>490.83584907859637</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="4">
         <f>Calculations!S37</f>
         <v>507.19704404788291</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="4">
         <f>Calculations!T37</f>
         <v>523.55823901716951</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="4">
         <f>Calculations!U37</f>
         <v>539.91943398645606</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="4">
         <f>Calculations!V37</f>
         <v>556.2806289557426</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="4">
         <f>Calculations!W37</f>
         <v>572.64182392502914</v>
       </c>
-      <c r="X2" s="5">
+      <c r="X2" s="4">
         <f>Calculations!X37</f>
         <v>589.00301889431569</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="4">
         <f>Calculations!Y37</f>
         <v>605.36421386360223</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="4">
         <f>Calculations!Z37</f>
         <v>621.72540883288877</v>
       </c>
-      <c r="AA2" s="5">
+      <c r="AA2" s="4">
         <f>Calculations!AA37</f>
         <v>638.08660380217532</v>
       </c>
-      <c r="AB2" s="5">
+      <c r="AB2" s="4">
         <f>Calculations!AB37</f>
         <v>654.44779877146186</v>
       </c>
-      <c r="AC2" s="5">
+      <c r="AC2" s="4">
         <f>Calculations!AC37</f>
         <v>670.80899374074841</v>
       </c>
-      <c r="AD2" s="5">
+      <c r="AD2" s="4">
         <f>Calculations!AD37</f>
         <v>687.17018871003495</v>
       </c>
-      <c r="AE2" s="5">
+      <c r="AE2" s="4">
         <f>Calculations!AE37</f>
         <v>703.53138367932149</v>
       </c>
-      <c r="AF2" s="5">
+      <c r="AF2" s="4">
         <f>Calculations!AF37</f>
         <v>719.89257864860804</v>
       </c>
-      <c r="AG2" s="5">
+      <c r="AG2" s="4">
         <f>Calculations!AG37</f>
         <v>736.25377361789458</v>
       </c>
@@ -7006,15 +6964,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="33" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="33" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B1">
@@ -7114,135 +7072,135 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <f>Calculations!B40</f>
         <v>0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <f>Calculations!C40</f>
         <v>285.55256753053982</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <f>Calculations!D40</f>
         <v>571.10513506107964</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <f>Calculations!E40</f>
         <v>856.65770259161945</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <f>Calculations!F40</f>
         <v>1142.2102701221593</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <f>Calculations!G40</f>
         <v>1427.7628376526991</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <f>Calculations!H40</f>
         <v>1713.3154051832389</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="4">
         <f>Calculations!I40</f>
         <v>1998.8679727137787</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <f>Calculations!J40</f>
         <v>2284.4205402443185</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="4">
         <f>Calculations!K40</f>
         <v>2569.9731077748584</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <f>Calculations!L40</f>
         <v>2855.5256753053982</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="4">
         <f>Calculations!M40</f>
         <v>3141.078242835938</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <f>Calculations!N40</f>
         <v>3426.6308103664778</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <f>Calculations!O40</f>
         <v>3712.1833778970176</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="4">
         <f>Calculations!P40</f>
         <v>3997.7359454275575</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="4">
         <f>Calculations!Q40</f>
         <v>4283.2885129580973</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <f>Calculations!R40</f>
         <v>4568.8410804886371</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="4">
         <f>Calculations!S40</f>
         <v>4870.8478462354897</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="4">
         <f>Calculations!T40</f>
         <v>5172.8546119823422</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="4">
         <f>Calculations!U40</f>
         <v>5474.8613777291948</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="4">
         <f>Calculations!V40</f>
         <v>5776.8681434760474</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="4">
         <f>Calculations!W40</f>
         <v>6078.8749092229</v>
       </c>
-      <c r="X2" s="5">
+      <c r="X2" s="4">
         <f>Calculations!X40</f>
         <v>6380.8816749697526</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="4">
         <f>Calculations!Y40</f>
         <v>6682.8884407166051</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="4">
         <f>Calculations!Z40</f>
         <v>6984.8952064634577</v>
       </c>
-      <c r="AA2" s="5">
+      <c r="AA2" s="4">
         <f>Calculations!AA40</f>
         <v>7286.9019722103103</v>
       </c>
-      <c r="AB2" s="5">
+      <c r="AB2" s="4">
         <f>Calculations!AB40</f>
         <v>7588.9087379571629</v>
       </c>
-      <c r="AC2" s="5">
+      <c r="AC2" s="4">
         <f>Calculations!AC40</f>
         <v>7890.9155037040155</v>
       </c>
-      <c r="AD2" s="5">
+      <c r="AD2" s="4">
         <f>Calculations!AD40</f>
         <v>8192.922269450868</v>
       </c>
-      <c r="AE2" s="5">
+      <c r="AE2" s="4">
         <f>Calculations!AE40</f>
         <v>8494.9290351977215</v>
       </c>
-      <c r="AF2" s="5">
+      <c r="AF2" s="4">
         <f>Calculations!AF40</f>
         <v>8796.935800944575</v>
       </c>
-      <c r="AG2" s="5">
+      <c r="AG2" s="4">
         <f>Calculations!AG40</f>
         <v>9098.9425666914321</v>
       </c>
@@ -7259,23 +7217,22 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.1640625" style="3" customWidth="1"/>
-    <col min="4" max="16384" width="9.1640625" style="3"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -7284,11 +7241,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B3" s="5"/>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC233EDB-B9F2-415D-B152-C4DFDBBACE57}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>